--- a/output/pdf_financials_xlsx/WHY.xlsx
+++ b/output/pdf_financials_xlsx/WHY.xlsx
@@ -8104,7 +8104,11 @@
           <t>Prepaid and deposits</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>PrepaidAssets</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/WHY.xlsx
+++ b/output/pdf_financials_xlsx/WHY.xlsx
@@ -975,10 +975,10 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.057974</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.001333</v>
       </c>
       <c r="D12" s="3" t="n">
         <v>0</v>
@@ -987,16 +987,16 @@
         <v>0</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>6.4e-05</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.000553</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.000295</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>0.000154</v>
       </c>
       <c r="J12" s="3" t="n">
         <v>0</v>
@@ -1821,10 +1821,10 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-2.227954</v>
+        <v>-2.285928</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-1.349982</v>
+        <v>-1.351315</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>-1.823247</v>
@@ -1833,16 +1833,16 @@
         <v>-1.15466</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-1.11695</v>
+        <v>-1.117014</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-0.816443</v>
+        <v>-0.8169960000000001</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-0.802108</v>
+        <v>-0.802403</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-1.277677</v>
+        <v>-1.277831</v>
       </c>
       <c r="J27" s="3" t="n">
         <v>-2.567341</v>
@@ -1925,10 +1925,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-2.180312</v>
+        <v>-2.238286</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-1.29704</v>
+        <v>-1.298373</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>-1.771799</v>
@@ -1937,16 +1937,16 @@
         <v>-1.114093</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-1.092035</v>
+        <v>-1.092099</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-0.797098</v>
+        <v>-0.797651</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-0.778179</v>
+        <v>-0.778474</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-1.274932</v>
+        <v>-1.275086</v>
       </c>
       <c r="J29" s="3" t="n">
         <v>-2.56668</v>
@@ -2236,13 +2236,13 @@
         <v>0.008857</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.168544</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.245393</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.431406</v>
       </c>
     </row>
     <row r="35">
@@ -2340,13 +2340,13 @@
         <v>0.008857</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.168544</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.245393</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>0.431406</v>
       </c>
     </row>
     <row r="37">
@@ -2964,13 +2964,13 @@
         <v>0.007979</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.247955</v>
+        <v>0.079411</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.294393</v>
+        <v>0.049</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.649367</v>
+        <v>0.217961</v>
       </c>
     </row>
     <row r="49">
@@ -7924,7 +7924,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -40248,7 +40248,7 @@
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E365" t="inlineStr">
@@ -41140,7 +41140,7 @@
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E375" t="inlineStr">
@@ -43804,7 +43804,7 @@
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E405" s="5" t="n">
